--- a/public/format_file_excel_import/disabilitas_pekerjaan.xlsx
+++ b/public/format_file_excel_import/disabilitas_pekerjaan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ariesyarwani/Documents/format excel import/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\Rumah data 2.0\public\format_file_excel_import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F547D13E-1FA2-364A-810E-F966CB5F6B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200EA845-D514-4591-A5A2-39B5732F0421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="1740" windowWidth="27240" windowHeight="16260" xr2:uid="{EFD8CF66-CCBF-964F-AA68-845B51AD6C11}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EFD8CF66-CCBF-964F-AA68-845B51AD6C11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -359,12 +357,6 @@
     <t>anggota_mahkamah_konstitusi_p</t>
   </si>
   <si>
-    <t>anggota_kabinet_kementrian_l</t>
-  </si>
-  <si>
-    <t>anggota_kabinet_kementrian_p</t>
-  </si>
-  <si>
     <t>duta_besar_l</t>
   </si>
   <si>
@@ -587,12 +579,6 @@
     <t>atlit_p</t>
   </si>
   <si>
-    <t>cheff_l</t>
-  </si>
-  <si>
-    <t>cheff_p</t>
-  </si>
-  <si>
     <t>manajer_l</t>
   </si>
   <si>
@@ -636,13 +622,25 @@
   </si>
   <si>
     <t>keterangan</t>
+  </si>
+  <si>
+    <t>anggota_kabinet_kementerian_l</t>
+  </si>
+  <si>
+    <t>anggota_kabinet_kementerian_p</t>
+  </si>
+  <si>
+    <t>chef_l</t>
+  </si>
+  <si>
+    <t>chef_p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -828,8 +826,8 @@
     <tableColumn id="106" xr3:uid="{54A7E005-394C-B44F-97DC-223133D9944F}" name="wakil_presiden_p"/>
     <tableColumn id="107" xr3:uid="{334A79D6-A5A9-4F49-AF94-0957DD74BA81}" name="anggota_mahkamah_konstitusi_l"/>
     <tableColumn id="108" xr3:uid="{6A066522-7C38-C144-8E38-8344A381CCB0}" name="anggota_mahkamah_konstitusi_p"/>
-    <tableColumn id="109" xr3:uid="{95D3A1B8-7894-9F41-9AC2-7470F806CEF5}" name="anggota_kabinet_kementrian_l"/>
-    <tableColumn id="110" xr3:uid="{7988AB08-3E81-6A40-A15E-B3E0252A9005}" name="anggota_kabinet_kementrian_p"/>
+    <tableColumn id="109" xr3:uid="{95D3A1B8-7894-9F41-9AC2-7470F806CEF5}" name="anggota_kabinet_kementerian_l"/>
+    <tableColumn id="110" xr3:uid="{7988AB08-3E81-6A40-A15E-B3E0252A9005}" name="anggota_kabinet_kementerian_p"/>
     <tableColumn id="111" xr3:uid="{4C65C72B-0CAA-0041-AF5D-BE3DC9733203}" name="duta_besar_l"/>
     <tableColumn id="112" xr3:uid="{DAFCB02B-FE53-9D43-A461-BFB654674E1A}" name="duta_besar_p"/>
     <tableColumn id="113" xr3:uid="{43A6CF43-8CF0-C943-9D81-2AD4E4354A1D}" name="gubernur_l"/>
@@ -904,8 +902,8 @@
     <tableColumn id="182" xr3:uid="{7BFA5840-61C3-C448-A458-426BD3B9EAC3}" name="artis_p"/>
     <tableColumn id="183" xr3:uid="{194C88F2-0ACF-F446-862E-86ED693D3027}" name="atlit_l"/>
     <tableColumn id="184" xr3:uid="{E56E172E-035F-DB4C-B7E3-24A5E698A530}" name="atlit_p"/>
-    <tableColumn id="185" xr3:uid="{4E526E6E-35E0-574C-B365-166E4BE1CF7A}" name="cheff_l"/>
-    <tableColumn id="186" xr3:uid="{C9665AE5-BD82-324A-95AF-73B930D13D05}" name="cheff_p"/>
+    <tableColumn id="185" xr3:uid="{4E526E6E-35E0-574C-B365-166E4BE1CF7A}" name="chef_l"/>
+    <tableColumn id="186" xr3:uid="{C9665AE5-BD82-324A-95AF-73B930D13D05}" name="chef_p"/>
     <tableColumn id="187" xr3:uid="{E2C7353E-83BE-D947-8FF0-2FB5F91E4755}" name="manajer_l"/>
     <tableColumn id="188" xr3:uid="{AA7E1D59-3643-FE45-9E28-012F83631E06}" name="manajer_p"/>
     <tableColumn id="189" xr3:uid="{0266C69B-DB47-4641-B74C-E6B0759A9609}" name="tenaga_tata_usaha_l"/>
@@ -1243,14 +1241,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71894179-9D4C-B441-B05A-CC84084F06A4}">
   <dimension ref="A1:GR2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:200" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:200">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1571,283 +1569,283 @@
         <v>106</v>
       </c>
       <c r="DE1" t="s">
+        <v>196</v>
+      </c>
+      <c r="DF1" t="s">
+        <v>197</v>
+      </c>
+      <c r="DG1" t="s">
         <v>107</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DH1" t="s">
         <v>108</v>
       </c>
-      <c r="DG1" t="s">
+      <c r="DI1" t="s">
         <v>109</v>
       </c>
-      <c r="DH1" t="s">
+      <c r="DJ1" t="s">
         <v>110</v>
       </c>
-      <c r="DI1" t="s">
+      <c r="DK1" t="s">
         <v>111</v>
       </c>
-      <c r="DJ1" t="s">
+      <c r="DL1" t="s">
         <v>112</v>
       </c>
-      <c r="DK1" t="s">
+      <c r="DM1" t="s">
         <v>113</v>
       </c>
-      <c r="DL1" t="s">
+      <c r="DN1" t="s">
         <v>114</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DO1" t="s">
         <v>115</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DP1" t="s">
         <v>116</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DQ1" t="s">
         <v>117</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DR1" t="s">
         <v>118</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DS1" t="s">
         <v>119</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DT1" t="s">
         <v>120</v>
       </c>
-      <c r="DS1" t="s">
+      <c r="DU1" t="s">
         <v>121</v>
       </c>
-      <c r="DT1" t="s">
+      <c r="DV1" t="s">
         <v>122</v>
       </c>
-      <c r="DU1" t="s">
+      <c r="DW1" t="s">
         <v>123</v>
       </c>
-      <c r="DV1" t="s">
+      <c r="DX1" t="s">
         <v>124</v>
       </c>
-      <c r="DW1" t="s">
+      <c r="DY1" t="s">
         <v>125</v>
       </c>
-      <c r="DX1" t="s">
+      <c r="DZ1" t="s">
         <v>126</v>
       </c>
-      <c r="DY1" t="s">
+      <c r="EA1" t="s">
         <v>127</v>
       </c>
-      <c r="DZ1" t="s">
+      <c r="EB1" t="s">
         <v>128</v>
       </c>
-      <c r="EA1" t="s">
+      <c r="EC1" t="s">
         <v>129</v>
       </c>
-      <c r="EB1" t="s">
+      <c r="ED1" t="s">
         <v>130</v>
       </c>
-      <c r="EC1" t="s">
+      <c r="EE1" t="s">
         <v>131</v>
       </c>
-      <c r="ED1" t="s">
+      <c r="EF1" t="s">
         <v>132</v>
       </c>
-      <c r="EE1" t="s">
+      <c r="EG1" t="s">
         <v>133</v>
       </c>
-      <c r="EF1" t="s">
+      <c r="EH1" t="s">
         <v>134</v>
       </c>
-      <c r="EG1" t="s">
+      <c r="EI1" t="s">
         <v>135</v>
       </c>
-      <c r="EH1" t="s">
+      <c r="EJ1" t="s">
         <v>136</v>
       </c>
-      <c r="EI1" t="s">
+      <c r="EK1" t="s">
         <v>137</v>
       </c>
-      <c r="EJ1" t="s">
+      <c r="EL1" t="s">
         <v>138</v>
       </c>
-      <c r="EK1" t="s">
+      <c r="EM1" t="s">
         <v>139</v>
       </c>
-      <c r="EL1" t="s">
+      <c r="EN1" t="s">
         <v>140</v>
       </c>
-      <c r="EM1" t="s">
+      <c r="EO1" t="s">
         <v>141</v>
       </c>
-      <c r="EN1" t="s">
+      <c r="EP1" t="s">
         <v>142</v>
       </c>
-      <c r="EO1" t="s">
+      <c r="EQ1" t="s">
         <v>143</v>
       </c>
-      <c r="EP1" t="s">
+      <c r="ER1" t="s">
         <v>144</v>
       </c>
-      <c r="EQ1" t="s">
+      <c r="ES1" t="s">
         <v>145</v>
       </c>
-      <c r="ER1" t="s">
+      <c r="ET1" t="s">
         <v>146</v>
       </c>
-      <c r="ES1" t="s">
+      <c r="EU1" t="s">
         <v>147</v>
       </c>
-      <c r="ET1" t="s">
+      <c r="EV1" t="s">
         <v>148</v>
       </c>
-      <c r="EU1" t="s">
+      <c r="EW1" t="s">
         <v>149</v>
       </c>
-      <c r="EV1" t="s">
+      <c r="EX1" t="s">
         <v>150</v>
       </c>
-      <c r="EW1" t="s">
+      <c r="EY1" t="s">
         <v>151</v>
       </c>
-      <c r="EX1" t="s">
+      <c r="EZ1" t="s">
         <v>152</v>
       </c>
-      <c r="EY1" t="s">
+      <c r="FA1" t="s">
         <v>153</v>
       </c>
-      <c r="EZ1" t="s">
+      <c r="FB1" t="s">
         <v>154</v>
       </c>
-      <c r="FA1" t="s">
+      <c r="FC1" t="s">
         <v>155</v>
       </c>
-      <c r="FB1" t="s">
+      <c r="FD1" t="s">
         <v>156</v>
       </c>
-      <c r="FC1" t="s">
+      <c r="FE1" t="s">
         <v>157</v>
       </c>
-      <c r="FD1" t="s">
+      <c r="FF1" t="s">
         <v>158</v>
       </c>
-      <c r="FE1" t="s">
+      <c r="FG1" t="s">
         <v>159</v>
       </c>
-      <c r="FF1" t="s">
+      <c r="FH1" t="s">
         <v>160</v>
       </c>
-      <c r="FG1" t="s">
+      <c r="FI1" t="s">
         <v>161</v>
       </c>
-      <c r="FH1" t="s">
+      <c r="FJ1" t="s">
         <v>162</v>
       </c>
-      <c r="FI1" t="s">
+      <c r="FK1" t="s">
         <v>163</v>
       </c>
-      <c r="FJ1" t="s">
+      <c r="FL1" t="s">
         <v>164</v>
       </c>
-      <c r="FK1" t="s">
+      <c r="FM1" t="s">
         <v>165</v>
       </c>
-      <c r="FL1" t="s">
+      <c r="FN1" t="s">
         <v>166</v>
       </c>
-      <c r="FM1" t="s">
+      <c r="FO1" t="s">
         <v>167</v>
       </c>
-      <c r="FN1" t="s">
+      <c r="FP1" t="s">
         <v>168</v>
       </c>
-      <c r="FO1" t="s">
+      <c r="FQ1" t="s">
         <v>169</v>
       </c>
-      <c r="FP1" t="s">
+      <c r="FR1" t="s">
         <v>170</v>
       </c>
-      <c r="FQ1" t="s">
+      <c r="FS1" t="s">
         <v>171</v>
       </c>
-      <c r="FR1" t="s">
+      <c r="FT1" t="s">
         <v>172</v>
       </c>
-      <c r="FS1" t="s">
+      <c r="FU1" t="s">
         <v>173</v>
       </c>
-      <c r="FT1" t="s">
+      <c r="FV1" t="s">
         <v>174</v>
       </c>
-      <c r="FU1" t="s">
+      <c r="FW1" t="s">
         <v>175</v>
       </c>
-      <c r="FV1" t="s">
+      <c r="FX1" t="s">
         <v>176</v>
       </c>
-      <c r="FW1" t="s">
+      <c r="FY1" t="s">
         <v>177</v>
       </c>
-      <c r="FX1" t="s">
+      <c r="FZ1" t="s">
         <v>178</v>
       </c>
-      <c r="FY1" t="s">
+      <c r="GA1" t="s">
         <v>179</v>
       </c>
-      <c r="FZ1" t="s">
+      <c r="GB1" t="s">
         <v>180</v>
       </c>
-      <c r="GA1" t="s">
+      <c r="GC1" t="s">
+        <v>198</v>
+      </c>
+      <c r="GD1" t="s">
+        <v>199</v>
+      </c>
+      <c r="GE1" t="s">
         <v>181</v>
       </c>
-      <c r="GB1" t="s">
+      <c r="GF1" t="s">
         <v>182</v>
       </c>
-      <c r="GC1" t="s">
+      <c r="GG1" t="s">
         <v>183</v>
       </c>
-      <c r="GD1" t="s">
+      <c r="GH1" t="s">
         <v>184</v>
       </c>
-      <c r="GE1" t="s">
+      <c r="GI1" t="s">
         <v>185</v>
       </c>
-      <c r="GF1" t="s">
+      <c r="GJ1" t="s">
         <v>186</v>
       </c>
-      <c r="GG1" t="s">
+      <c r="GK1" t="s">
         <v>187</v>
       </c>
-      <c r="GH1" t="s">
+      <c r="GL1" t="s">
         <v>188</v>
       </c>
-      <c r="GI1" t="s">
+      <c r="GM1" t="s">
         <v>189</v>
       </c>
-      <c r="GJ1" t="s">
+      <c r="GN1" t="s">
         <v>190</v>
       </c>
-      <c r="GK1" t="s">
+      <c r="GO1" t="s">
         <v>191</v>
       </c>
-      <c r="GL1" t="s">
+      <c r="GP1" t="s">
         <v>192</v>
       </c>
-      <c r="GM1" t="s">
+      <c r="GQ1" t="s">
         <v>193</v>
       </c>
-      <c r="GN1" t="s">
+      <c r="GR1" t="s">
         <v>194</v>
       </c>
-      <c r="GO1" t="s">
-        <v>195</v>
-      </c>
-      <c r="GP1" t="s">
-        <v>196</v>
-      </c>
-      <c r="GQ1" t="s">
-        <v>197</v>
-      </c>
-      <c r="GR1" t="s">
-        <v>198</v>
-      </c>
     </row>
-    <row r="2" spans="1:200" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:200" ht="15.75">
       <c r="A2" s="1"/>
     </row>
   </sheetData>
